--- a/data/dimensions/dim_municipio.xlsx
+++ b/data/dimensions/dim_municipio.xlsx
@@ -238,7 +238,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,14 +369,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -725,7 +717,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1060,6 +1052,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1080,7 +1077,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1091,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1102,7 +1099,7 @@
         <v>54</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1113,7 +1110,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1124,7 +1121,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1135,7 +1132,7 @@
         <v>11</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1146,7 +1143,7 @@
         <v>12</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1157,7 +1154,7 @@
         <v>61</v>
       </c>
       <c r="C9">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1168,7 +1165,7 @@
         <v>55</v>
       </c>
       <c r="C10">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1179,7 +1176,7 @@
         <v>13</v>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1190,7 +1187,7 @@
         <v>14</v>
       </c>
       <c r="C12">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1201,7 +1198,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1212,7 +1209,7 @@
         <v>62</v>
       </c>
       <c r="C14">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1223,7 +1220,7 @@
         <v>16</v>
       </c>
       <c r="C15">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1234,7 +1231,7 @@
         <v>17</v>
       </c>
       <c r="C16">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1245,7 +1242,7 @@
         <v>18</v>
       </c>
       <c r="C17">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1256,7 +1253,7 @@
         <v>19</v>
       </c>
       <c r="C18">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1267,7 +1264,7 @@
         <v>20</v>
       </c>
       <c r="C19">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1278,7 +1275,7 @@
         <v>21</v>
       </c>
       <c r="C20">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1289,7 +1286,7 @@
         <v>56</v>
       </c>
       <c r="C21">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1300,7 +1297,7 @@
         <v>22</v>
       </c>
       <c r="C22">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1311,7 +1308,7 @@
         <v>23</v>
       </c>
       <c r="C23">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1322,7 +1319,7 @@
         <v>24</v>
       </c>
       <c r="C24">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1333,7 +1330,7 @@
         <v>57</v>
       </c>
       <c r="C25">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1344,7 +1341,7 @@
         <v>25</v>
       </c>
       <c r="C26">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1355,7 +1352,7 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1366,7 +1363,7 @@
         <v>26</v>
       </c>
       <c r="C28">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1377,7 +1374,7 @@
         <v>27</v>
       </c>
       <c r="C29">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1388,7 +1385,7 @@
         <v>59</v>
       </c>
       <c r="C30">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1399,7 +1396,7 @@
         <v>28</v>
       </c>
       <c r="C31">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1410,7 +1407,7 @@
         <v>29</v>
       </c>
       <c r="C32">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1421,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="C33">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1432,7 +1429,7 @@
         <v>31</v>
       </c>
       <c r="C34">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1443,7 +1440,7 @@
         <v>32</v>
       </c>
       <c r="C35">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1454,7 +1451,7 @@
         <v>18</v>
       </c>
       <c r="C36">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1465,7 +1462,7 @@
         <v>33</v>
       </c>
       <c r="C37">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1476,7 +1473,7 @@
         <v>34</v>
       </c>
       <c r="C38">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1487,7 +1484,7 @@
         <v>35</v>
       </c>
       <c r="C39">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1498,7 +1495,7 @@
         <v>4</v>
       </c>
       <c r="C40">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1509,7 +1506,7 @@
         <v>36</v>
       </c>
       <c r="C41">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1520,7 +1517,7 @@
         <v>37</v>
       </c>
       <c r="C42">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1531,7 +1528,7 @@
         <v>38</v>
       </c>
       <c r="C43">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1542,7 +1539,7 @@
         <v>58</v>
       </c>
       <c r="C44">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1553,7 +1550,7 @@
         <v>39</v>
       </c>
       <c r="C45">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1564,7 +1561,7 @@
         <v>40</v>
       </c>
       <c r="C46">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1575,7 +1572,7 @@
         <v>68</v>
       </c>
       <c r="C47">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1586,7 +1583,7 @@
         <v>3</v>
       </c>
       <c r="C48">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1597,7 +1594,7 @@
         <v>41</v>
       </c>
       <c r="C49">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1608,7 +1605,7 @@
         <v>66</v>
       </c>
       <c r="C50">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1619,7 +1616,7 @@
         <v>69</v>
       </c>
       <c r="C51">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1630,7 +1627,7 @@
         <v>70</v>
       </c>
       <c r="C52">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1641,7 +1638,7 @@
         <v>42</v>
       </c>
       <c r="C53">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1652,7 +1649,7 @@
         <v>43</v>
       </c>
       <c r="C54">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1663,7 +1660,7 @@
         <v>44</v>
       </c>
       <c r="C55">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1674,7 +1671,7 @@
         <v>67</v>
       </c>
       <c r="C56">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1685,7 +1682,7 @@
         <v>45</v>
       </c>
       <c r="C57">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1696,7 +1693,7 @@
         <v>46</v>
       </c>
       <c r="C58">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1707,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="C59">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1718,7 +1715,7 @@
         <v>48</v>
       </c>
       <c r="C60">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1729,7 +1726,7 @@
         <v>49</v>
       </c>
       <c r="C61">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1740,7 +1737,7 @@
         <v>5</v>
       </c>
       <c r="C62">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1751,7 +1748,7 @@
         <v>63</v>
       </c>
       <c r="C63">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1762,7 +1759,7 @@
         <v>60</v>
       </c>
       <c r="C64">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1773,7 +1770,7 @@
         <v>50</v>
       </c>
       <c r="C65">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1784,7 +1781,7 @@
         <v>64</v>
       </c>
       <c r="C66">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1795,7 +1792,7 @@
         <v>51</v>
       </c>
       <c r="C67">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1806,7 +1803,7 @@
         <v>52</v>
       </c>
       <c r="C68">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -1817,7 +1814,7 @@
         <v>65</v>
       </c>
       <c r="C69">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -1828,7 +1825,7 @@
         <v>53</v>
       </c>
       <c r="C70">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1836,5 +1833,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>